--- a/prafta-ai-stack/corpus/registry/sources.xlsx
+++ b/prafta-ai-stack/corpus/registry/sources.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
@@ -656,6 +656,11 @@
           <t>data_reliability</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>api_fixed_params</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,7 +1319,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://apis.data.go.kr/B552468/disaster_api02</t>
+          <t>https://apis.data.go.kr/B552468/disaster_api02/getdisaster_api02</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>raw/15121001_kosha_disaster_YYYYMMDD.json</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1334,7 +1344,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>산업안전(재해사례)</t>
+          <t>제조업</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1362,22 +1372,32 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>keyword,contents</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>business</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>제목, 등록일</t>
+          <t>boardno</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>business, boardno, 등록일</t>
+          <t>business,boardno,atcflcnt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>집계형</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>callApiId=1060</t>
         </is>
       </c>
     </row>

--- a/prafta-ai-stack/corpus/registry/sources.xlsx
+++ b/prafta-ai-stack/corpus/registry/sources.xlsx
@@ -1172,7 +1172,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>data.go.kr 이용허락범위 '제한 없음'(웹확인 2026-07-05). CSV 약 1,026행. 사고업체명·상세주소 실명 필드 포함 → 마스킹 필요. 사람 최종확인(license_checked→TRUE) 전까지 파이프라인 자동 적재 제외.</t>
+          <t>이용허락범위 제한없음(웹확인 2026-07-05). CSV 1,026행 전량 파싱 확인(제외 0건, 2026-08-26). 사고업체명·상세주소 실명 필드 포함 → 마스킹 필수 적용됨(2026-08-26): 본문(content)은 known-value 퍼지매칭(공백 양방향 무시)으로 회사명 치환, META_JSON 사고업체명은 패턴매칭 없이 무조건 "○○" 치환(공용 masking.py/preprocess.py 개선 — 건설업 접미사 위주 _COMPANY 정규식이 화학/제조업 회사명을 못 잡던 문제 해소, 1,026건 전수 감사로 잔여 누출 0건 확인).</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://apis.data.go.kr/B552468/disaster_attach_api02</t>
+          <t>https://apis.data.go.kr/B552468/disaster_attach_api02/Disaster_attach_api02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1467,32 +1467,42 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>제한 없음(웹확인 2026-07-05). 15121001 과 boardno 로 연계. 첨부 PDF(사고개요/발생원인/예방대책 구조) 파싱 필요. 스키마 미검증. 사람 최종확인(license_checked→TRUE) 전까지 파이프라인 자동 적재 제외.</t>
+          <t>15121001과 boardno로 연계된 KOSHA OPS 첨부 PDF(재해개요/발생원인/예방대책 2단 구성). 이용허락범위 제한없음(15121001과 동일 기관·동일 확인, 웹확인 2026-07-05). 엔드포인트/파라미터 실측 확정(2026-08-26): 서브패스 Disaster_attach_api02(대문자) + callApiId=1070. 좌우 컬럼 x좌표 크롭으로 발생원인/예방대책 분리 파싱(20_collect_disaster_attach.py + preprocess.py read_disaster_attach_pdf). 재해개요는 15121001에 이미 있어 중복 방지 위해 content에서 제외, 발생원인만 CONTENT로.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>cause_text</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>예방대책</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>기인물</t>
+          <t>measure_text</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>business</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>boardno, 파일명</t>
+          <t>boardno</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>boardno, 파일명</t>
+          <t>boardno, filenm</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
           <t>집계형</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>callApiId=1070</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1529,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://apis.data.go.kr/B552468/koshaguide</t>
+          <t>https://apis.data.go.kr/B552468/koshaguide/getKoshaGuide</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>raw/15144147_koshaguide_YYYYMMDD.json</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1562,32 +1577,37 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>API 이용허락범위 '제한 없음'(웹확인 2026-07-05). API는 규정명/번호/공표일/PDF 다운로드 링크만 제공 → 가이드 PDF 본문 파싱 필요(수백 건). 가이드 문서 자체 이용조건은 미확인(문서 내 고지 확인 필요). 스키마 미검증. 사람 최종확인(license_checked→TRUE) 전까지 파이프라인 자동 적재 제외.</t>
+          <t>이용허락범위 제한없음(API 등록 기준, 웹확인 2026-08-27). 실측(2026-08-27): 엔드포인트 .../koshaguide/getKoshaGuide(camelCase) + callApiId=1050, 총 1,039건(A~X 등 14개 계열). 링크된 가이드 PDF 4건(A/D/D-C 계열) 확인 결과 공공누리 마크 자체가 없음(제한 문구도 없음) — MOEL 정책자료실(4유형 다수 확인)과 달리 이 API는 data.go.kr에 공식 개방 데이터로 등록돼 있어 위험도 낮다고 판단, 사람 확인 하에 진행. 문서 내부가 길어(12~200p) 목차/번호 섹션(1./2./4.1/5.2 등) 기준 청킹 필요 — collect_koshaguide_pdf.py + preprocess.py read_koshaguide_pdf 참조.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>규정명</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>안전조치 조항</t>
+          <t>section_text</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>techGdlnNo_prefix</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>규정번호, 규정명</t>
+          <t>techGdlnNo,section_no</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>규정번호, 규정공표일자, 다운로드링크</t>
+          <t>techGdlnNo, techGdlnNm, techGdlnOfancYmd, section_title</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>집계형</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>callApiId=1050</t>
         </is>
       </c>
     </row>

--- a/prafta-ai-stack/corpus/registry/sources.xlsx
+++ b/prafta-ai-stack/corpus/registry/sources.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="12"/>
@@ -661,6 +661,11 @@
           <t>api_fixed_params</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>evidence_tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -770,6 +775,11 @@
           <t>집계형</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -885,6 +895,11 @@
       <c r="Y3" s="7" t="inlineStr">
         <is>
           <t>자율신고형</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>CASE</t>
         </is>
       </c>
     </row>
@@ -996,6 +1011,11 @@
           <t>집계형</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>STAT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1105,6 +1125,11 @@
           <t>집계형</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>REF</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1205,6 +1230,11 @@
           <t>집계형</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1400,6 +1430,11 @@
           <t>callApiId=1060</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1505,6 +1540,11 @@
           <t>callApiId=1070</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>CASE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1610,6 +1650,11 @@
           <t>callApiId=1050</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>GUIDE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1708,6 +1753,666 @@
       <c r="Y11" t="inlineStr">
         <is>
           <t>집계형</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LAW_OSHA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>산업안전보건법</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/법령/산업안전보건법</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/DRF/lawService.do</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>raw/LAW_OSHA_law_283449_YYYYMMDD.xml</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>공공누리 제1유형</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>verbatim</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>법령-산안법</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>수시(개정시)</t>
+        </is>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-09-02 data.go.kr 15000115 활용신청·제1유형 확인(메인 세션). 본문은 law.go.kr DRF(lawService.do, OC 인증) — 22_collect_law_articles.py 전용(collect_api.py 대상 아님). ★track=verbatim 사유는 라이선스가 아니라 정확성(정책서 §4.5 사유 2갈래 — LLM 조문 날조 구조적 차단). MST 는 개정마다 바뀌므로 api_fixed_params 에만 두고 source_id 에 넣지 않는다(개정 감지 --check-revision).</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>article_text</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>_domain</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>law_id, mst, law_name, law_kind, ministry, promulgation_date, law_effective_date, article_effective_date, article_no, article_branch_no, article_title, article_changed</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>법령</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>target=law&amp;MST=283449</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LAW_OSHA_ENF</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>산업안전보건법 시행령</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/법령/산업안전보건법시행령</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/DRF/lawService.do</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>raw/LAW_OSHA_ENF_law_288347_YYYYMMDD.xml</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>공공누리 제1유형</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>verbatim</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>법령-시행령</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>수시(개정시)</t>
+        </is>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-09-02 data.go.kr 15000115 활용신청·제1유형 확인(메인 세션). 본문은 law.go.kr DRF(lawService.do, OC 인증) — 22_collect_law_articles.py 전용(collect_api.py 대상 아님). ★track=verbatim 사유는 라이선스가 아니라 정확성(정책서 §4.5 사유 2갈래 — LLM 조문 날조 구조적 차단). MST 는 개정마다 바뀌므로 api_fixed_params 에만 두고 source_id 에 넣지 않는다(개정 감지 --check-revision).</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>article_text</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>_domain</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>law_id, mst, law_name, law_kind, ministry, promulgation_date, law_effective_date, article_effective_date, article_no, article_branch_no, article_title, article_changed</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>법령</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>target=law&amp;MST=288347</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LAW_OSHA_RULE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>산업안전보건법 시행규칙</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/법령/산업안전보건법시행규칙</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/DRF/lawService.do</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>raw/LAW_OSHA_RULE_law_288431_YYYYMMDD.xml</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>공공누리 제1유형</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>verbatim</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>법령-시행규칙</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>수시(개정시)</t>
+        </is>
+      </c>
+      <c r="M14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-09-02 data.go.kr 15000115 활용신청·제1유형 확인(메인 세션). 본문은 law.go.kr DRF(lawService.do, OC 인증) — 22_collect_law_articles.py 전용(collect_api.py 대상 아님). ★track=verbatim 사유는 라이선스가 아니라 정확성(정책서 §4.5 사유 2갈래 — LLM 조문 날조 구조적 차단). MST 는 개정마다 바뀌므로 api_fixed_params 에만 두고 source_id 에 넣지 않는다(개정 감지 --check-revision).</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>article_text</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>_domain</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>law_id, mst, law_name, law_kind, ministry, promulgation_date, law_effective_date, article_effective_date, article_no, article_branch_no, article_title, article_changed</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>법령</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>target=law&amp;MST=288431</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LAW_OSHA_STD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>산업안전보건기준에 관한 규칙</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/법령/산업안전보건기준에관한규칙</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/DRF/lawService.do</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>raw/LAW_OSHA_STD_law_273603_YYYYMMDD.xml</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>공공누리 제1유형</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>verbatim</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>법령-안전보건규칙</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>수시(개정시)</t>
+        </is>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-09-02 data.go.kr 15000115 활용신청·제1유형 확인(메인 세션). 본문은 law.go.kr DRF(lawService.do, OC 인증) — 22_collect_law_articles.py 전용(collect_api.py 대상 아님). ★track=verbatim 사유는 라이선스가 아니라 정확성(정책서 §4.5 사유 2갈래 — LLM 조문 날조 구조적 차단). MST 는 개정마다 바뀌므로 api_fixed_params 에만 두고 source_id 에 넣지 않는다(개정 감지 --check-revision).</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>article_text</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>_domain</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>law_id, mst, law_name, law_kind, ministry, promulgation_date, law_effective_date, article_effective_date, article_no, article_branch_no, article_title, article_changed</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>법령</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>target=law&amp;MST=273603</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LAW_SAPA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>중대재해 처벌 등에 관한 법률</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/법령/중대재해처벌등에관한법률</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/DRF/lawService.do</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>raw/LAW_SAPA_law_228817_YYYYMMDD.xml</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>공공누리 제1유형</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>verbatim</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>법령-중대재해법</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>수시(개정시)</t>
+        </is>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-09-02 data.go.kr 15000115 활용신청·제1유형 확인(메인 세션). 본문은 law.go.kr DRF(lawService.do, OC 인증) — 22_collect_law_articles.py 전용(collect_api.py 대상 아님). ★track=verbatim 사유는 라이선스가 아니라 정확성(정책서 §4.5 사유 2갈래 — LLM 조문 날조 구조적 차단). MST 는 개정마다 바뀌므로 api_fixed_params 에만 두고 source_id 에 넣지 않는다(개정 감지 --check-revision).</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>article_text</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>_domain</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>law_id, mst, law_name, law_kind, ministry, promulgation_date, law_effective_date, article_effective_date, article_no, article_branch_no, article_title, article_changed</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>법령</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>target=law&amp;MST=228817</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>LAW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LAW_SAPA_ENF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>법제처</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>중대재해 처벌 등에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/법령/중대재해처벌법시행령</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.law.go.kr/DRF/lawService.do</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>raw/LAW_SAPA_ENF_law_277417_YYYYMMDD.xml</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>utf-8</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>공공누리 제1유형</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>verbatim</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>법령-중대재해령</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>수시(개정시)</t>
+        </is>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-09-02 data.go.kr 15000115 활용신청·제1유형 확인(메인 세션). 본문은 law.go.kr DRF(lawService.do, OC 인증) — 22_collect_law_articles.py 전용(collect_api.py 대상 아님). ★track=verbatim 사유는 라이선스가 아니라 정확성(정책서 §4.5 사유 2갈래 — LLM 조문 날조 구조적 차단). MST 는 개정마다 바뀌므로 api_fixed_params 에만 두고 source_id 에 넣지 않는다(개정 감지 --check-revision).</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>article_text</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>_domain</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>locator</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>law_id, mst, law_name, law_kind, ministry, promulgation_date, law_effective_date, article_effective_date, article_no, article_branch_no, article_title, article_changed</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>법령</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>target=law&amp;MST=277417</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>LAW</t>
         </is>
       </c>
     </row>
